--- a/Data/collapsed database manual cases/jalisco_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/jalisco_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CCF144-523E-C648-A56F-97AA25FACED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13234C5-53FA-7C42-87CC-340EADF370A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10737" uniqueCount="1999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10748" uniqueCount="2003">
   <si>
     <t>uniqueid</t>
   </si>
@@ -6020,6 +6020,18 @@
   </si>
   <si>
     <t>Magar</t>
+  </si>
+  <si>
+    <t>CI_1</t>
+  </si>
+  <si>
+    <t>OSCAR DANIEL CARRION CALVARIO</t>
+  </si>
+  <si>
+    <t>https://www.milenio.com/politica/comunidad/alcalde-sayula-ejercio-violencia-politica-razon-genero</t>
+  </si>
+  <si>
+    <t>GALA DEL CARMEN LEPE GALVAN</t>
   </si>
 </sst>
 </file>
@@ -6415,7 +6427,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S1045"/>
+  <dimension ref="A1:S1047"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -52451,7 +52463,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="1041" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1041" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1041">
         <v>14054</v>
       </c>
@@ -52474,7 +52486,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="1042" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1042" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1042">
         <v>14065</v>
       </c>
@@ -52497,7 +52509,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="1043" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1043" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1043">
         <v>14095</v>
       </c>
@@ -52520,7 +52532,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="1044" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1044" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1044">
         <v>14123</v>
       </c>
@@ -52543,7 +52555,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="1045" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1045" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1045">
         <v>14052</v>
       </c>
@@ -52564,6 +52576,55 @@
       </c>
       <c r="I1045" t="s">
         <v>1998</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1046">
+        <v>14082</v>
+      </c>
+      <c r="B1046">
+        <v>2021</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1046" t="s">
+        <v>2001</v>
+      </c>
+      <c r="J1046" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1046" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1047">
+        <v>14110</v>
+      </c>
+      <c r="B1047">
+        <v>2021</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H1047" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1047" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1047" t="s">
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
